--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925789</v>
+        <v>131925340</v>
       </c>
       <c r="B4" t="n">
-        <v>57905</v>
+        <v>79267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R4" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,17 +999,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925340</v>
+        <v>131925789</v>
       </c>
       <c r="B5" t="n">
-        <v>79267</v>
+        <v>57905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,37 +1017,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R5" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -787,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925883</v>
+        <v>131925340</v>
       </c>
       <c r="B3" t="n">
-        <v>5178</v>
+        <v>79267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R3" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,52 +887,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925340</v>
+        <v>131925883</v>
       </c>
       <c r="B4" t="n">
-        <v>79267</v>
+        <v>5178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R4" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1449,32 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131925269</v>
+        <v>131926162</v>
       </c>
       <c r="B9" t="n">
-        <v>79291</v>
+        <v>99045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473548</v>
+        <v>473620</v>
       </c>
       <c r="R9" t="n">
-        <v>6780115</v>
+        <v>6780083</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Några ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,44 +1549,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131926162</v>
+        <v>131925269</v>
       </c>
       <c r="B10" t="n">
-        <v>99045</v>
+        <v>79291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,13 +1596,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473620</v>
+        <v>473548</v>
       </c>
       <c r="R10" t="n">
-        <v>6780083</v>
+        <v>6780115</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,12 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Några ex</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -787,45 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925340</v>
+        <v>131925883</v>
       </c>
       <c r="B3" t="n">
-        <v>79267</v>
+        <v>5178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R3" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,57 +892,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925883</v>
+        <v>131925340</v>
       </c>
       <c r="B4" t="n">
-        <v>5178</v>
+        <v>79267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R4" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131925894</v>
       </c>
       <c r="B2" t="n">
-        <v>99045</v>
+        <v>99047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,38 +787,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925883</v>
+        <v>131925789</v>
       </c>
       <c r="B3" t="n">
-        <v>5178</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>6780119</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131925340</v>
       </c>
       <c r="B4" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,38 +1006,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925789</v>
+        <v>131925883</v>
       </c>
       <c r="B5" t="n">
-        <v>57905</v>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,7 +1052,7 @@
         <v>6780119</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>131925299</v>
       </c>
       <c r="B6" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131925198</v>
       </c>
       <c r="B7" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>131925475</v>
       </c>
       <c r="B8" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,32 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131926162</v>
+        <v>131925269</v>
       </c>
       <c r="B9" t="n">
-        <v>99045</v>
+        <v>79293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473620</v>
+        <v>473548</v>
       </c>
       <c r="R9" t="n">
-        <v>6780083</v>
+        <v>6780115</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,12 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några ex</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,44 +1544,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131925269</v>
+        <v>131926162</v>
       </c>
       <c r="B10" t="n">
-        <v>79291</v>
+        <v>99047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,13 +1591,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473548</v>
+        <v>473620</v>
       </c>
       <c r="R10" t="n">
-        <v>6780115</v>
+        <v>6780083</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1636,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Några ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131925894</v>
       </c>
       <c r="B2" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925789</v>
+        <v>131925340</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R3" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,17 +887,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925340</v>
+        <v>131925789</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +905,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R4" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
         <v>131925299</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131925198</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131925269</v>
       </c>
       <c r="B9" t="n">
-        <v>79293</v>
+        <v>79298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131926162</v>
       </c>
       <c r="B10" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925340</v>
+        <v>131925789</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R3" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +892,45 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925789</v>
+        <v>131925883</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -940,7 +945,7 @@
         <v>6780119</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,50 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925883</v>
+        <v>131925340</v>
       </c>
       <c r="B5" t="n">
-        <v>5179</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R5" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131925894</v>
       </c>
       <c r="B2" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131925789</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131925340</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>131925299</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131925198</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131925269</v>
       </c>
       <c r="B9" t="n">
-        <v>79298</v>
+        <v>79300</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131926162</v>
       </c>
       <c r="B10" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131925894</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131925340</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>131925299</v>
       </c>
       <c r="B6" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131925198</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131925269</v>
       </c>
       <c r="B9" t="n">
-        <v>79339</v>
+        <v>79341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131926162</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -1449,32 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131925269</v>
+        <v>131926162</v>
       </c>
       <c r="B9" t="n">
-        <v>79341</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473548</v>
+        <v>473620</v>
       </c>
       <c r="R9" t="n">
-        <v>6780115</v>
+        <v>6780083</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1529,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Några ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,44 +1549,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131926162</v>
+        <v>131925269</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>79341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,13 +1596,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473620</v>
+        <v>473548</v>
       </c>
       <c r="R10" t="n">
-        <v>6780083</v>
+        <v>6780115</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,12 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Några ex</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -1449,32 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131926162</v>
+        <v>131925269</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>79341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473620</v>
+        <v>473548</v>
       </c>
       <c r="R9" t="n">
-        <v>6780083</v>
+        <v>6780115</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,12 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några ex</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,44 +1544,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131925269</v>
+        <v>131926162</v>
       </c>
       <c r="B10" t="n">
-        <v>79341</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,13 +1591,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473548</v>
+        <v>473620</v>
       </c>
       <c r="R10" t="n">
-        <v>6780115</v>
+        <v>6780083</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1636,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Några ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131925894</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925340</v>
+        <v>131925789</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R3" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +892,45 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925789</v>
+        <v>131925883</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -940,7 +945,7 @@
         <v>6780119</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,50 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925883</v>
+        <v>131925340</v>
       </c>
       <c r="B5" t="n">
-        <v>5179</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R5" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
         <v>131925299</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131925198</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>131926162</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>131925269</v>
       </c>
       <c r="B10" t="n">
-        <v>79341</v>
+        <v>79343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925789</v>
+        <v>131925340</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>79319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R3" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,45 +887,45 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925883</v>
+        <v>131925789</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,7 +940,7 @@
         <v>6780119</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,45 +1006,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925340</v>
+        <v>131925883</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R5" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131925894</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131925340</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131925789</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>131925299</v>
       </c>
       <c r="B6" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131925198</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,32 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131926162</v>
+        <v>131925269</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>79351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473620</v>
+        <v>473548</v>
       </c>
       <c r="R9" t="n">
-        <v>6780083</v>
+        <v>6780115</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,12 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Några ex</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,44 +1544,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131925269</v>
+        <v>131926162</v>
       </c>
       <c r="B10" t="n">
-        <v>79343</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,13 +1591,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473548</v>
+        <v>473620</v>
       </c>
       <c r="R10" t="n">
-        <v>6780115</v>
+        <v>6780083</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1636,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Några ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,12 +1656,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925340</v>
+        <v>131925789</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473583</v>
+        <v>473637</v>
       </c>
       <c r="R3" t="n">
-        <v>6780097</v>
+        <v>6780119</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,45 +892,45 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925789</v>
+        <v>131925883</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -940,7 +945,7 @@
         <v>6780119</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,50 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925883</v>
+        <v>131925340</v>
       </c>
       <c r="B5" t="n">
-        <v>5179</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R5" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131925894</v>
+        <v>131925198</v>
       </c>
       <c r="B2" t="n">
-        <v>99116</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473637</v>
+        <v>473535</v>
       </c>
       <c r="R2" t="n">
-        <v>6780119</v>
+        <v>6780118</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,60 +775,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131925789</v>
+        <v>131925299</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473637</v>
+        <v>473548</v>
       </c>
       <c r="R3" t="n">
-        <v>6780119</v>
+        <v>6780115</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,57 +882,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131925883</v>
+        <v>131925340</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473637</v>
+        <v>473583</v>
       </c>
       <c r="R4" t="n">
-        <v>6780119</v>
+        <v>6780097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,21 +989,21 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131925340</v>
+        <v>131925568</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1046,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473583</v>
+        <v>473590</v>
       </c>
       <c r="R5" t="n">
-        <v>6780097</v>
+        <v>6780036</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131925299</v>
+        <v>131925269</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>79397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,7 +1144,7 @@
         <v>6780115</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131925198</v>
+        <v>131925789</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,37 +1221,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473535</v>
+        <v>473637</v>
       </c>
       <c r="R7" t="n">
-        <v>6780118</v>
+        <v>6780119</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,17 +1315,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131925475</v>
+        <v>131925883</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>5181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,27 +1333,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1372,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473620</v>
+        <v>473637</v>
       </c>
       <c r="R8" t="n">
-        <v>6780083</v>
+        <v>6780119</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,12 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,22 +1422,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131925269</v>
+        <v>131925475</v>
       </c>
       <c r="B9" t="n">
-        <v>79351</v>
+        <v>8460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,37 +1445,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473548</v>
+        <v>473620</v>
       </c>
       <c r="R9" t="n">
-        <v>6780115</v>
+        <v>6780083</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1519,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1539,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131926162</v>
+        <v>131925894</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,19 +1580,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rädmyren, Rädmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473620</v>
+        <v>473637</v>
       </c>
       <c r="R10" t="n">
-        <v>6780083</v>
+        <v>6780119</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,12 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Några ex</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,15 +1651,127 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131926162</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rädmyren, Rädmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>473620</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6780083</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Några ex</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Peter Turander</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Peter Turander</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10693-2026 artfynd.xlsx
+++ b/artfynd/A 10693-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925299</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925568</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925269</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925883</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925475</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131925894</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,8 +1822,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131926162</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>